--- a/docs/analysis/system-operations/SO_예약상태관리.xlsx
+++ b/docs/analysis/system-operations/SO_예약상태관리.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wonsik/Documents/3_1_season/소프트웨어공학/sw-project/SO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KANG\Desktop\sw-project-v1\SO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA759D26-CBDA-0A4B-A3BD-F978276C7FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AE7772-4727-40CA-95FF-2D347BD3C666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5900" yWindow="1060" windowWidth="28100" windowHeight="17080" activeTab="2" xr2:uid="{0F0F4B5A-B31D-AC46-B157-1760E77E2349}"/>
+    <workbookView xWindow="6930" yWindow="720" windowWidth="15195" windowHeight="14895" firstSheet="1" activeTab="2" xr2:uid="{0F0F4B5A-B31D-AC46-B157-1760E77E2349}"/>
   </bookViews>
   <sheets>
     <sheet name="getPendingReservations" sheetId="3" r:id="rId1"/>
@@ -41,17 +41,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="29">
   <si>
     <t>항목</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>내용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -167,7 +163,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -710,14 +706,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{682D2E14-C178-474B-92DD-4E9885792D70}">
-  <dimension ref="B2:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <dimension ref="B2:C11"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="3" max="3" width="65.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="3" max="3" width="65.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -725,87 +721,73 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5"/>
-    </row>
-    <row r="4" spans="2:3" ht="19">
+      <c r="C3" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" ht="19">
-      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" ht="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" ht="19">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3">
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="5"/>
-    </row>
-    <row r="9" spans="2:3" ht="19">
-      <c r="B9" s="1" t="s">
+      <c r="C8" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="19">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B10" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3">
-      <c r="B11" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="6"/>
-    </row>
-    <row r="12" spans="2:3">
-      <c r="B12" s="12"/>
-      <c r="C12" s="6"/>
-    </row>
-    <row r="13" spans="2:3">
-      <c r="B13" s="12"/>
-      <c r="C13" s="7"/>
-    </row>
-    <row r="14" spans="2:3">
-      <c r="B14" s="13"/>
-      <c r="C14" s="8"/>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B11" s="13"/>
+      <c r="C11" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -814,14 +796,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{863F0C0D-79AD-A140-ADFE-B56658C5F632}">
-  <dimension ref="B2:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <dimension ref="B2:C11"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="3" max="3" width="65.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="3" max="3" width="65.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -829,91 +811,77 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5"/>
-    </row>
-    <row r="4" spans="2:3" ht="19">
+      <c r="C3" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" ht="19">
-      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" ht="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3">
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="2:3" ht="19">
+      <c r="C7" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="19">
-      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="19">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B10" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B11" s="13"/>
+      <c r="C11" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" ht="19">
-      <c r="B11" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" ht="19">
-      <c r="B12" s="12"/>
-      <c r="C12" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3">
-      <c r="B13" s="12"/>
-      <c r="C13" s="7"/>
-    </row>
-    <row r="14" spans="2:3">
-      <c r="B14" s="13"/>
-      <c r="C14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -922,14 +890,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B8A3AF-F399-DC48-972C-B5242B2A1594}">
-  <dimension ref="B2:C15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <dimension ref="B2:C14"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="3" max="3" width="65.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="3" max="3" width="65.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -937,100 +905,94 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5"/>
-    </row>
-    <row r="4" spans="2:3" ht="19">
+      <c r="C3" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" ht="19">
-      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" ht="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3">
-      <c r="B7" s="1" t="s">
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B7" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="2:3" ht="19">
-      <c r="B8" s="14" t="s">
+      <c r="C7" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B8" s="15"/>
+      <c r="C8" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="19">
-      <c r="B9" s="15"/>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="19">
-      <c r="B10" s="1" t="s">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B11" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B12" s="12"/>
+      <c r="C12" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="19">
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" ht="19">
-      <c r="B12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" ht="19">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13" s="12"/>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="19">
-      <c r="B14" s="12"/>
-      <c r="C14" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3">
-      <c r="B15" s="13"/>
-      <c r="C15" s="8"/>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B14" s="13"/>
+      <c r="C14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="B7:B8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
